--- a/ptu-neogenesis-foundry-compendiums/movimientos.xlsx
+++ b/ptu-neogenesis-foundry-compendiums/movimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\ptu-neogenesis\ptu-neogenesis-foundry-compendiums\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AE8615-B4F7-4B5C-B531-F2D53D2F5D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD0A3D3-59D2-45CD-AD7E-0EDC13C8674C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{446E682F-B129-484C-926D-5AE9D0F56FFF}"/>
   </bookViews>
@@ -8010,7 +8010,7 @@
       <c r="S28" s="21"/>
       <c r="T28" s="22"/>
     </row>
-    <row r="29" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>102</v>
       </c>
@@ -9624,7 +9624,7 @@
       <c r="S66" s="21"/>
       <c r="T66" s="22"/>
     </row>
-    <row r="67" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>209</v>
       </c>
@@ -9838,7 +9838,7 @@
       <c r="S71" s="21"/>
       <c r="T71" s="22"/>
     </row>
-    <row r="72" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>217</v>
       </c>
@@ -10416,7 +10416,7 @@
       <c r="S85" s="21"/>
       <c r="T85" s="22"/>
     </row>
-    <row r="86" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>256</v>
       </c>
@@ -11402,7 +11402,7 @@
       <c r="S108" s="21"/>
       <c r="T108" s="22"/>
     </row>
-    <row r="109" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>318</v>
       </c>
@@ -12964,7 +12964,7 @@
       <c r="S145" s="21"/>
       <c r="T145" s="22"/>
     </row>
-    <row r="146" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>416</v>
       </c>
@@ -14554,7 +14554,7 @@
       <c r="S183" s="21"/>
       <c r="T183" s="22"/>
     </row>
-    <row r="184" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>503</v>
       </c>
@@ -15738,7 +15738,7 @@
       <c r="S211" s="21"/>
       <c r="T211" s="22"/>
     </row>
-    <row r="212" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>576</v>
       </c>
@@ -17916,7 +17916,7 @@
       <c r="S263" s="21"/>
       <c r="T263" s="22"/>
     </row>
-    <row r="264" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>684</v>
       </c>
@@ -21832,7 +21832,7 @@
       <c r="S356" s="21"/>
       <c r="T356" s="22"/>
     </row>
-    <row r="357" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
         <v>894</v>
       </c>
@@ -22758,7 +22758,7 @@
       <c r="S377" s="21"/>
       <c r="T377" s="22"/>
     </row>
-    <row r="378" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>934</v>
       </c>
@@ -28524,7 +28524,7 @@
       <c r="S515" s="21"/>
       <c r="T515" s="22"/>
     </row>
-    <row r="516" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
         <v>1248</v>
       </c>
@@ -31000,7 +31000,7 @@
       <c r="S575" s="21"/>
       <c r="T575" s="22"/>
     </row>
-    <row r="576" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
         <v>1378</v>
       </c>
@@ -32416,7 +32416,7 @@
       <c r="S609" s="21"/>
       <c r="T609" s="22"/>
     </row>
-    <row r="610" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
         <v>1443</v>
       </c>
@@ -34788,7 +34788,7 @@
       <c r="S667" s="21"/>
       <c r="T667" s="22"/>
     </row>
-    <row r="668" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
         <v>1569</v>
       </c>
@@ -36998,7 +36998,7 @@
       <c r="S720" s="21"/>
       <c r="T720" s="22"/>
     </row>
-    <row r="721" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
         <v>1670</v>
       </c>
@@ -38642,7 +38642,7 @@
       <c r="S759" s="21"/>
       <c r="T759" s="22"/>
     </row>
-    <row r="760" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
         <v>1743</v>
       </c>
@@ -39574,7 +39574,7 @@
       <c r="S781" s="21"/>
       <c r="T781" s="22"/>
     </row>
-    <row r="782" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
         <v>1787</v>
       </c>
@@ -39824,7 +39824,7 @@
       <c r="S787" s="21"/>
       <c r="T787" s="22"/>
     </row>
-    <row r="788" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
         <v>1799</v>
       </c>
@@ -40362,7 +40362,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="801" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A801" s="3" t="s">
         <v>1829</v>
       </c>
@@ -41020,7 +41020,7 @@
       <c r="S816" s="21"/>
       <c r="T816" s="22"/>
     </row>
-    <row r="817" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A817" s="3" t="s">
         <v>1859</v>
       </c>
@@ -41652,7 +41652,7 @@
       <c r="S831" s="21"/>
       <c r="T831" s="22"/>
     </row>
-    <row r="832" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A832" s="3" t="s">
         <v>1893</v>
       </c>
@@ -43058,7 +43058,7 @@
       <c r="S864" s="21"/>
       <c r="T864" s="22"/>
     </row>
-    <row r="865" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A865" s="3" t="s">
         <v>1952</v>
       </c>
